--- a/public/sap-reporting/expansion-150-downloads/EXT-CO21-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-CO21-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rc3f5a144dcdb42f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rab75cadd6ecc4b08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R16079a9f89894874"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rec5d9c1414fa4690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R136855c9f0b649b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R4cad96ce85bd45a8"/>
   </x:sheets>
 </x:workbook>
 </file>
